--- a/artfynd/A 39718-2024 artfynd.xlsx
+++ b/artfynd/A 39718-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,6 +1027,3941 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129926723</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>65</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>444348</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6924034</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129926722</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>444366</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6924005</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129926699</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>444138</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6923625</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129926725</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>444315</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6923974</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129926727</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>444295</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6923949</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129926707</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78839</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>444272</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6923791</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>129926714</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91772</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>444331</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6923827</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>129926731</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78839</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>444190</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6923908</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>129926700</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78839</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>444139</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6923624</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129926726</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>444309</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6923959</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:27</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129926729</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>444210</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6923955</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129926718</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97667</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>444362</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6923872</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129926705</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>444117</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6923735</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129926698</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>444118</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6923621</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129926715</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92241</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5454</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Hornvaxskinn</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Crustoderma corneum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>444350</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6923880</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129926734</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78747</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>353</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>444169</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6923886</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129926704</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80222</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>444124</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6923727</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129926710</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92881</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>444283</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6923819</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129926721</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>444365</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6923915</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129926720</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91772</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>444360</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6923918</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129926706</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90422</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>444279</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6923782</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129926724</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78839</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>444330</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6923984</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129926728</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91652</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>444229</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6923882</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129926702</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>444122</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6923680</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129926701</v>
+      </c>
+      <c r="B29" t="n">
+        <v>105856</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>444126</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6923694</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129926709</v>
+      </c>
+      <c r="B30" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>444268</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6923829</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129926730</v>
+      </c>
+      <c r="B31" t="n">
+        <v>78484</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>444200</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6923914</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129926733</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>444163</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6923898</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129926713</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91522</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>444347</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6923828</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Under grov, gammal nedfallen tallgren.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129926736</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>444093</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6923866</v>
+      </c>
+      <c r="S34" t="n">
+        <v>4</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129926703</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>444124</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6923712</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129926717</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91613</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>444352</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6923879</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>129926735</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91772</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>444143</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6923881</v>
+      </c>
+      <c r="S37" t="n">
+        <v>4</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129926716</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91772</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>444351</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6923878</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129926708</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Högfjället, Hjd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>444257</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6923818</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Greensway AB</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Mellanskog AB - Högfjället</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39718-2024 artfynd.xlsx
+++ b/artfynd/A 39718-2024 artfynd.xlsx
@@ -1029,32 +1029,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129926723</v>
+        <v>129926699</v>
       </c>
       <c r="B5" t="n">
-        <v>91872</v>
+        <v>79674</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444348</v>
+        <v>444138</v>
       </c>
       <c r="R5" t="n">
-        <v>6924034</v>
+        <v>6923625</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,7 +1143,7 @@
         <v>129926722</v>
       </c>
       <c r="B6" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,32 +1251,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129926699</v>
+        <v>129926723</v>
       </c>
       <c r="B7" t="n">
-        <v>79671</v>
+        <v>91875</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444138</v>
+        <v>444348</v>
       </c>
       <c r="R7" t="n">
-        <v>6923625</v>
+        <v>6924034</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,7 +1365,7 @@
         <v>129926725</v>
       </c>
       <c r="B8" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
         <v>129926727</v>
       </c>
       <c r="B9" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>129926707</v>
       </c>
       <c r="B10" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,32 +1695,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129926714</v>
+        <v>129926731</v>
       </c>
       <c r="B11" t="n">
-        <v>91772</v>
+        <v>78842</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444331</v>
+        <v>444190</v>
       </c>
       <c r="R11" t="n">
-        <v>6923827</v>
+        <v>6923908</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,10 +1806,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129926731</v>
+        <v>129926700</v>
       </c>
       <c r="B12" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444190</v>
+        <v>444139</v>
       </c>
       <c r="R12" t="n">
-        <v>6923908</v>
+        <v>6923624</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,32 +1917,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129926700</v>
+        <v>129926714</v>
       </c>
       <c r="B13" t="n">
-        <v>78839</v>
+        <v>91775</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444139</v>
+        <v>444331</v>
       </c>
       <c r="R13" t="n">
-        <v>6923624</v>
+        <v>6923827</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2031,7 +2031,7 @@
         <v>129926726</v>
       </c>
       <c r="B14" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>129926729</v>
       </c>
       <c r="B15" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,32 +2259,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129926718</v>
+        <v>129926698</v>
       </c>
       <c r="B16" t="n">
-        <v>97667</v>
+        <v>79674</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444362</v>
+        <v>444118</v>
       </c>
       <c r="R16" t="n">
-        <v>6923872</v>
+        <v>6923621</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2373,7 +2373,7 @@
         <v>129926705</v>
       </c>
       <c r="B17" t="n">
-        <v>80221</v>
+        <v>80224</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,32 +2481,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926698</v>
+        <v>129926718</v>
       </c>
       <c r="B18" t="n">
-        <v>79671</v>
+        <v>97671</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444118</v>
+        <v>444362</v>
       </c>
       <c r="R18" t="n">
-        <v>6923621</v>
+        <v>6923872</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2595,7 +2595,7 @@
         <v>129926715</v>
       </c>
       <c r="B19" t="n">
-        <v>92241</v>
+        <v>92244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>129926734</v>
       </c>
       <c r="B20" t="n">
-        <v>78747</v>
+        <v>78750</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129926704</v>
+        <v>129926710</v>
       </c>
       <c r="B21" t="n">
-        <v>80222</v>
+        <v>92884</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,34 +2825,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444124</v>
+        <v>444283</v>
       </c>
       <c r="R21" t="n">
-        <v>6923727</v>
+        <v>6923819</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2884,7 +2893,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2894,7 +2903,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2934,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129926710</v>
+        <v>129926704</v>
       </c>
       <c r="B22" t="n">
-        <v>92881</v>
+        <v>80225</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2936,43 +2945,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444283</v>
+        <v>444124</v>
       </c>
       <c r="R22" t="n">
-        <v>6923819</v>
+        <v>6923727</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3045,32 +3045,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B23" t="n">
-        <v>79671</v>
+        <v>91775</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R23" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,32 +3156,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B24" t="n">
-        <v>91772</v>
+        <v>79674</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R24" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3270,7 +3270,7 @@
         <v>129926706</v>
       </c>
       <c r="B25" t="n">
-        <v>90422</v>
+        <v>90425</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3390,7 +3390,7 @@
         <v>129926724</v>
       </c>
       <c r="B26" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129926728</v>
+        <v>129926709</v>
       </c>
       <c r="B27" t="n">
-        <v>91652</v>
+        <v>91525</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3509,21 +3509,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3533,13 +3533,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444229</v>
+        <v>444268</v>
       </c>
       <c r="R27" t="n">
-        <v>6923882</v>
+        <v>6923829</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,54 +3609,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129926702</v>
+        <v>129926701</v>
       </c>
       <c r="B28" t="n">
-        <v>98790</v>
+        <v>105860</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444122</v>
+        <v>444126</v>
       </c>
       <c r="R28" t="n">
-        <v>6923680</v>
+        <v>6923694</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3729,32 +3720,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129926701</v>
+        <v>129926728</v>
       </c>
       <c r="B29" t="n">
-        <v>105856</v>
+        <v>91655</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3764,10 +3755,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444126</v>
+        <v>444229</v>
       </c>
       <c r="R29" t="n">
-        <v>6923694</v>
+        <v>6923882</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3799,7 +3790,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3800,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3840,48 +3831,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129926709</v>
+        <v>129926702</v>
       </c>
       <c r="B30" t="n">
-        <v>91522</v>
+        <v>98794</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444268</v>
+        <v>444122</v>
       </c>
       <c r="R30" t="n">
-        <v>6923829</v>
+        <v>6923680</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3910,7 +3910,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3954,7 +3954,7 @@
         <v>129926730</v>
       </c>
       <c r="B31" t="n">
-        <v>78484</v>
+        <v>78487</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>129926733</v>
       </c>
       <c r="B32" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>129926713</v>
       </c>
       <c r="B33" t="n">
-        <v>91522</v>
+        <v>91525</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4289,45 +4289,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926736</v>
+        <v>129926703</v>
       </c>
       <c r="B34" t="n">
-        <v>78838</v>
+        <v>98794</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444093</v>
+        <v>444124</v>
       </c>
       <c r="R34" t="n">
-        <v>6923866</v>
+        <v>6923712</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4359,7 +4368,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4369,7 +4378,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4400,54 +4409,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926703</v>
+        <v>129926736</v>
       </c>
       <c r="B35" t="n">
-        <v>98790</v>
+        <v>78841</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444124</v>
+        <v>444093</v>
       </c>
       <c r="R35" t="n">
-        <v>6923712</v>
+        <v>6923866</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4523,7 +4523,7 @@
         <v>129926717</v>
       </c>
       <c r="B36" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>129926735</v>
       </c>
       <c r="B37" t="n">
-        <v>91772</v>
+        <v>91775</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>129926716</v>
       </c>
       <c r="B38" t="n">
-        <v>91772</v>
+        <v>91775</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>129926708</v>
       </c>
       <c r="B39" t="n">
-        <v>79671</v>
+        <v>79674</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 39718-2024 artfynd.xlsx
+++ b/artfynd/A 39718-2024 artfynd.xlsx
@@ -1029,32 +1029,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129926699</v>
+        <v>129926722</v>
       </c>
       <c r="B5" t="n">
-        <v>79674</v>
+        <v>92884</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444138</v>
+        <v>444366</v>
       </c>
       <c r="R5" t="n">
-        <v>6923625</v>
+        <v>6924005</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,32 +1140,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129926722</v>
+        <v>129926725</v>
       </c>
       <c r="B6" t="n">
-        <v>92884</v>
+        <v>79703</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444366</v>
+        <v>444315</v>
       </c>
       <c r="R6" t="n">
-        <v>6924005</v>
+        <v>6923974</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1362,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129926725</v>
+        <v>129926699</v>
       </c>
       <c r="B8" t="n">
-        <v>79703</v>
+        <v>79674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444315</v>
+        <v>444138</v>
       </c>
       <c r="R8" t="n">
-        <v>6923974</v>
+        <v>6923625</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129926727</v>
+        <v>129926707</v>
       </c>
       <c r="B9" t="n">
-        <v>79674</v>
+        <v>78842</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444295</v>
+        <v>444272</v>
       </c>
       <c r="R9" t="n">
-        <v>6923949</v>
+        <v>6923791</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129926707</v>
+        <v>129926727</v>
       </c>
       <c r="B10" t="n">
-        <v>78842</v>
+        <v>79674</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,21 +1595,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444272</v>
+        <v>444295</v>
       </c>
       <c r="R10" t="n">
-        <v>6923791</v>
+        <v>6923949</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,32 +1695,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129926731</v>
+        <v>129926714</v>
       </c>
       <c r="B11" t="n">
-        <v>78842</v>
+        <v>91775</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444190</v>
+        <v>444331</v>
       </c>
       <c r="R11" t="n">
-        <v>6923908</v>
+        <v>6923827</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,7 +1806,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129926700</v>
+        <v>129926731</v>
       </c>
       <c r="B12" t="n">
         <v>78842</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444139</v>
+        <v>444190</v>
       </c>
       <c r="R12" t="n">
-        <v>6923624</v>
+        <v>6923908</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,32 +1917,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129926714</v>
+        <v>129926700</v>
       </c>
       <c r="B13" t="n">
-        <v>91775</v>
+        <v>78842</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444331</v>
+        <v>444139</v>
       </c>
       <c r="R13" t="n">
-        <v>6923827</v>
+        <v>6923624</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2259,32 +2259,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129926698</v>
+        <v>129926705</v>
       </c>
       <c r="B16" t="n">
-        <v>79674</v>
+        <v>80224</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,13 +2294,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444118</v>
+        <v>444117</v>
       </c>
       <c r="R16" t="n">
-        <v>6923621</v>
+        <v>6923735</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129926705</v>
+        <v>129926718</v>
       </c>
       <c r="B17" t="n">
-        <v>80224</v>
+        <v>97671</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2381,21 +2381,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444117</v>
+        <v>444362</v>
       </c>
       <c r="R17" t="n">
-        <v>6923735</v>
+        <v>6923872</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,32 +2481,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129926718</v>
+        <v>129926698</v>
       </c>
       <c r="B18" t="n">
-        <v>97671</v>
+        <v>79674</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>229821</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2516,10 +2516,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>444362</v>
+        <v>444118</v>
       </c>
       <c r="R18" t="n">
-        <v>6923872</v>
+        <v>6923621</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2551,7 +2551,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3045,32 +3045,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B23" t="n">
-        <v>91775</v>
+        <v>79674</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R23" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,32 +3156,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B24" t="n">
-        <v>79674</v>
+        <v>91775</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R24" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3498,10 +3498,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129926709</v>
+        <v>129926728</v>
       </c>
       <c r="B27" t="n">
-        <v>91525</v>
+        <v>91655</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3509,21 +3509,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3533,13 +3533,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444268</v>
+        <v>444229</v>
       </c>
       <c r="R27" t="n">
-        <v>6923829</v>
+        <v>6923882</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,32 +3609,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129926701</v>
+        <v>129926709</v>
       </c>
       <c r="B28" t="n">
-        <v>105860</v>
+        <v>91525</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>3242</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3644,13 +3644,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444126</v>
+        <v>444268</v>
       </c>
       <c r="R28" t="n">
-        <v>6923694</v>
+        <v>6923829</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3720,45 +3720,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129926728</v>
+        <v>129926702</v>
       </c>
       <c r="B29" t="n">
-        <v>91655</v>
+        <v>98794</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444229</v>
+        <v>444122</v>
       </c>
       <c r="R29" t="n">
-        <v>6923882</v>
+        <v>6923680</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3790,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3800,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,54 +3840,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129926702</v>
+        <v>129926701</v>
       </c>
       <c r="B30" t="n">
-        <v>98794</v>
+        <v>105860</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444122</v>
+        <v>444126</v>
       </c>
       <c r="R30" t="n">
-        <v>6923680</v>
+        <v>6923694</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4289,54 +4289,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926703</v>
+        <v>129926736</v>
       </c>
       <c r="B34" t="n">
-        <v>98794</v>
+        <v>78841</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444124</v>
+        <v>444093</v>
       </c>
       <c r="R34" t="n">
-        <v>6923712</v>
+        <v>6923866</v>
       </c>
       <c r="S34" t="n">
         <v>4</v>
@@ -4368,7 +4359,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4378,7 +4369,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4409,45 +4400,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129926736</v>
+        <v>129926703</v>
       </c>
       <c r="B35" t="n">
-        <v>78841</v>
+        <v>98794</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444093</v>
+        <v>444124</v>
       </c>
       <c r="R35" t="n">
-        <v>6923866</v>
+        <v>6923712</v>
       </c>
       <c r="S35" t="n">
         <v>4</v>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 39718-2024 artfynd.xlsx
+++ b/artfynd/A 39718-2024 artfynd.xlsx
@@ -1029,32 +1029,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129926722</v>
+        <v>129926723</v>
       </c>
       <c r="B5" t="n">
-        <v>92884</v>
+        <v>91875</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444366</v>
+        <v>444348</v>
       </c>
       <c r="R5" t="n">
-        <v>6924005</v>
+        <v>6924034</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1251,32 +1251,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129926723</v>
+        <v>129926722</v>
       </c>
       <c r="B7" t="n">
-        <v>91875</v>
+        <v>92884</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444348</v>
+        <v>444366</v>
       </c>
       <c r="R7" t="n">
-        <v>6924034</v>
+        <v>6924005</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129926707</v>
+        <v>129926727</v>
       </c>
       <c r="B9" t="n">
-        <v>78842</v>
+        <v>79674</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444272</v>
+        <v>444295</v>
       </c>
       <c r="R9" t="n">
-        <v>6923791</v>
+        <v>6923949</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129926727</v>
+        <v>129926707</v>
       </c>
       <c r="B10" t="n">
-        <v>79674</v>
+        <v>78842</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,21 +1595,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444295</v>
+        <v>444272</v>
       </c>
       <c r="R10" t="n">
-        <v>6923949</v>
+        <v>6923791</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,32 +1695,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129926714</v>
+        <v>129926731</v>
       </c>
       <c r="B11" t="n">
-        <v>91775</v>
+        <v>78842</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444331</v>
+        <v>444190</v>
       </c>
       <c r="R11" t="n">
-        <v>6923827</v>
+        <v>6923908</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,7 +1806,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129926731</v>
+        <v>129926700</v>
       </c>
       <c r="B12" t="n">
         <v>78842</v>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444190</v>
+        <v>444139</v>
       </c>
       <c r="R12" t="n">
-        <v>6923908</v>
+        <v>6923624</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,32 +1917,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129926700</v>
+        <v>129926714</v>
       </c>
       <c r="B13" t="n">
-        <v>78842</v>
+        <v>91775</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444139</v>
+        <v>444331</v>
       </c>
       <c r="R13" t="n">
-        <v>6923624</v>
+        <v>6923827</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3045,32 +3045,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B23" t="n">
-        <v>79674</v>
+        <v>91775</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R23" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,32 +3156,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B24" t="n">
-        <v>91775</v>
+        <v>79674</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R24" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -4173,10 +4173,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129926713</v>
+        <v>129926736</v>
       </c>
       <c r="B33" t="n">
-        <v>91525</v>
+        <v>78841</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444347</v>
+        <v>444093</v>
       </c>
       <c r="R33" t="n">
-        <v>6923828</v>
+        <v>6923866</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4253,12 +4253,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Under grov, gammal nedfallen tallgren.</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4289,10 +4284,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926736</v>
+        <v>129926713</v>
       </c>
       <c r="B34" t="n">
-        <v>78841</v>
+        <v>91525</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,21 +4295,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4324,13 +4319,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444093</v>
+        <v>444347</v>
       </c>
       <c r="R34" t="n">
-        <v>6923866</v>
+        <v>6923828</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4359,7 +4354,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4369,7 +4364,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Under grov, gammal nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 39718-2024 artfynd.xlsx
+++ b/artfynd/A 39718-2024 artfynd.xlsx
@@ -1029,32 +1029,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129926723</v>
+        <v>129926725</v>
       </c>
       <c r="B5" t="n">
-        <v>91875</v>
+        <v>79706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444348</v>
+        <v>444315</v>
       </c>
       <c r="R5" t="n">
-        <v>6924034</v>
+        <v>6923974</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,32 +1140,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129926725</v>
+        <v>129926723</v>
       </c>
       <c r="B6" t="n">
-        <v>79703</v>
+        <v>91878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444315</v>
+        <v>444348</v>
       </c>
       <c r="R6" t="n">
-        <v>6923974</v>
+        <v>6924034</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,7 +1254,7 @@
         <v>129926722</v>
       </c>
       <c r="B7" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>129926699</v>
       </c>
       <c r="B8" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129926727</v>
+        <v>129926707</v>
       </c>
       <c r="B9" t="n">
-        <v>79674</v>
+        <v>78845</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444295</v>
+        <v>444272</v>
       </c>
       <c r="R9" t="n">
-        <v>6923949</v>
+        <v>6923791</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129926707</v>
+        <v>129926727</v>
       </c>
       <c r="B10" t="n">
-        <v>78842</v>
+        <v>79677</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,21 +1595,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444272</v>
+        <v>444295</v>
       </c>
       <c r="R10" t="n">
-        <v>6923791</v>
+        <v>6923949</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,7 +1698,7 @@
         <v>129926731</v>
       </c>
       <c r="B11" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1809,7 +1809,7 @@
         <v>129926700</v>
       </c>
       <c r="B12" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>129926714</v>
       </c>
       <c r="B13" t="n">
-        <v>91775</v>
+        <v>91778</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>129926726</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         <v>129926729</v>
       </c>
       <c r="B15" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2262,7 +2262,7 @@
         <v>129926705</v>
       </c>
       <c r="B16" t="n">
-        <v>80224</v>
+        <v>80227</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>129926718</v>
       </c>
       <c r="B17" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>129926698</v>
       </c>
       <c r="B18" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>129926715</v>
       </c>
       <c r="B19" t="n">
-        <v>92244</v>
+        <v>92247</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>129926734</v>
       </c>
       <c r="B20" t="n">
-        <v>78750</v>
+        <v>78753</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129926710</v>
       </c>
       <c r="B21" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>129926704</v>
       </c>
       <c r="B22" t="n">
-        <v>80225</v>
+        <v>80228</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,32 +3045,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B23" t="n">
-        <v>91775</v>
+        <v>79677</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R23" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,32 +3156,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B24" t="n">
-        <v>79674</v>
+        <v>91778</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R24" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3267,57 +3267,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129926706</v>
+        <v>129926724</v>
       </c>
       <c r="B25" t="n">
-        <v>90425</v>
+        <v>78845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6286</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444279</v>
+        <v>444330</v>
       </c>
       <c r="R25" t="n">
-        <v>6923782</v>
+        <v>6923984</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3346,7 +3337,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3356,7 +3347,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3387,48 +3378,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129926724</v>
+        <v>129926706</v>
       </c>
       <c r="B26" t="n">
-        <v>78842</v>
+        <v>90428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444330</v>
+        <v>444279</v>
       </c>
       <c r="R26" t="n">
-        <v>6923984</v>
+        <v>6923782</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3498,10 +3498,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129926728</v>
+        <v>129926709</v>
       </c>
       <c r="B27" t="n">
-        <v>91655</v>
+        <v>91528</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3509,21 +3509,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3533,13 +3533,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444229</v>
+        <v>444268</v>
       </c>
       <c r="R27" t="n">
-        <v>6923882</v>
+        <v>6923829</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,48 +3609,57 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129926709</v>
+        <v>129926702</v>
       </c>
       <c r="B28" t="n">
-        <v>91525</v>
+        <v>98797</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444268</v>
+        <v>444122</v>
       </c>
       <c r="R28" t="n">
-        <v>6923829</v>
+        <v>6923680</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3679,7 +3688,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3689,7 +3698,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3720,54 +3729,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129926702</v>
+        <v>129926728</v>
       </c>
       <c r="B29" t="n">
-        <v>98794</v>
+        <v>91658</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444122</v>
+        <v>444229</v>
       </c>
       <c r="R29" t="n">
-        <v>6923680</v>
+        <v>6923882</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3799,7 +3799,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3843,7 +3843,7 @@
         <v>129926701</v>
       </c>
       <c r="B30" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3951,10 +3951,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129926730</v>
+        <v>129926733</v>
       </c>
       <c r="B31" t="n">
-        <v>78487</v>
+        <v>79677</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3962,21 +3962,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444200</v>
+        <v>444163</v>
       </c>
       <c r="R31" t="n">
-        <v>6923914</v>
+        <v>6923898</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129926733</v>
+        <v>129926730</v>
       </c>
       <c r="B32" t="n">
-        <v>79674</v>
+        <v>78490</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4073,21 +4073,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444163</v>
+        <v>444200</v>
       </c>
       <c r="R32" t="n">
-        <v>6923898</v>
+        <v>6923914</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4173,10 +4173,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129926736</v>
+        <v>129926713</v>
       </c>
       <c r="B33" t="n">
-        <v>78841</v>
+        <v>91528</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444093</v>
+        <v>444347</v>
       </c>
       <c r="R33" t="n">
-        <v>6923866</v>
+        <v>6923828</v>
       </c>
       <c r="S33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4253,7 +4253,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Under grov, gammal nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4284,10 +4289,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926713</v>
+        <v>129926736</v>
       </c>
       <c r="B34" t="n">
-        <v>91525</v>
+        <v>78844</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4295,21 +4300,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4319,13 +4324,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444347</v>
+        <v>444093</v>
       </c>
       <c r="R34" t="n">
-        <v>6923828</v>
+        <v>6923866</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4354,7 +4359,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4364,12 +4369,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Under grov, gammal nedfallen tallgren.</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4403,7 +4403,7 @@
         <v>129926703</v>
       </c>
       <c r="B35" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>129926717</v>
       </c>
       <c r="B36" t="n">
-        <v>91616</v>
+        <v>91619</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>129926735</v>
       </c>
       <c r="B37" t="n">
-        <v>91775</v>
+        <v>91778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4742,32 +4742,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129926716</v>
+        <v>129926708</v>
       </c>
       <c r="B38" t="n">
-        <v>91775</v>
+        <v>79677</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4777,10 +4777,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444351</v>
+        <v>444257</v>
       </c>
       <c r="R38" t="n">
-        <v>6923878</v>
+        <v>6923818</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4853,32 +4853,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129926708</v>
+        <v>129926716</v>
       </c>
       <c r="B39" t="n">
-        <v>79674</v>
+        <v>91778</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444257</v>
+        <v>444351</v>
       </c>
       <c r="R39" t="n">
-        <v>6923818</v>
+        <v>6923878</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 39718-2024 artfynd.xlsx
+++ b/artfynd/A 39718-2024 artfynd.xlsx
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129926705</v>
+        <v>129926718</v>
       </c>
       <c r="B16" t="n">
-        <v>80227</v>
+        <v>97674</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,13 +2294,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444117</v>
+        <v>444362</v>
       </c>
       <c r="R16" t="n">
-        <v>6923735</v>
+        <v>6923872</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129926718</v>
+        <v>129926705</v>
       </c>
       <c r="B17" t="n">
-        <v>97674</v>
+        <v>80227</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2381,21 +2381,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444362</v>
+        <v>444117</v>
       </c>
       <c r="R17" t="n">
-        <v>6923872</v>
+        <v>6923735</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3045,32 +3045,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129926721</v>
+        <v>129926720</v>
       </c>
       <c r="B23" t="n">
-        <v>79677</v>
+        <v>91778</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444365</v>
+        <v>444360</v>
       </c>
       <c r="R23" t="n">
-        <v>6923915</v>
+        <v>6923918</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3156,32 +3156,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129926720</v>
+        <v>129926721</v>
       </c>
       <c r="B24" t="n">
-        <v>91778</v>
+        <v>79677</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3191,10 +3191,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444360</v>
+        <v>444365</v>
       </c>
       <c r="R24" t="n">
-        <v>6923918</v>
+        <v>6923915</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 39718-2024 artfynd.xlsx
+++ b/artfynd/A 39718-2024 artfynd.xlsx
@@ -2814,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129926710</v>
+        <v>129926704</v>
       </c>
       <c r="B21" t="n">
-        <v>92887</v>
+        <v>80228</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2825,43 +2825,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444283</v>
+        <v>444124</v>
       </c>
       <c r="R21" t="n">
-        <v>6923819</v>
+        <v>6923727</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2893,7 +2884,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2903,7 +2894,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2934,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129926704</v>
+        <v>129926710</v>
       </c>
       <c r="B22" t="n">
-        <v>80228</v>
+        <v>92887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2945,34 +2936,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444124</v>
+        <v>444283</v>
       </c>
       <c r="R22" t="n">
-        <v>6923727</v>
+        <v>6923819</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3951,10 +3951,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129926733</v>
+        <v>129926730</v>
       </c>
       <c r="B31" t="n">
-        <v>79677</v>
+        <v>78490</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3962,21 +3962,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3986,10 +3986,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444163</v>
+        <v>444200</v>
       </c>
       <c r="R31" t="n">
-        <v>6923898</v>
+        <v>6923914</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4062,10 +4062,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129926730</v>
+        <v>129926733</v>
       </c>
       <c r="B32" t="n">
-        <v>78490</v>
+        <v>79677</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4073,21 +4073,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4097,10 +4097,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444200</v>
+        <v>444163</v>
       </c>
       <c r="R32" t="n">
-        <v>6923914</v>
+        <v>6923898</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 39718-2024 artfynd.xlsx
+++ b/artfynd/A 39718-2024 artfynd.xlsx
@@ -1029,32 +1029,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129926725</v>
+        <v>129926723</v>
       </c>
       <c r="B5" t="n">
-        <v>79706</v>
+        <v>91879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444315</v>
+        <v>444348</v>
       </c>
       <c r="R5" t="n">
-        <v>6923974</v>
+        <v>6924034</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,32 +1140,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129926723</v>
+        <v>129926725</v>
       </c>
       <c r="B6" t="n">
-        <v>91878</v>
+        <v>79707</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444348</v>
+        <v>444315</v>
       </c>
       <c r="R6" t="n">
-        <v>6924034</v>
+        <v>6923974</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,32 +1251,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129926722</v>
+        <v>129926699</v>
       </c>
       <c r="B7" t="n">
-        <v>92887</v>
+        <v>79678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444366</v>
+        <v>444138</v>
       </c>
       <c r="R7" t="n">
-        <v>6924005</v>
+        <v>6923625</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,32 +1362,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129926699</v>
+        <v>129926722</v>
       </c>
       <c r="B8" t="n">
-        <v>79677</v>
+        <v>92888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444138</v>
+        <v>444366</v>
       </c>
       <c r="R8" t="n">
-        <v>6923625</v>
+        <v>6924005</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129926707</v>
+        <v>129926727</v>
       </c>
       <c r="B9" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1484,21 +1484,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1508,13 +1508,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>444272</v>
+        <v>444295</v>
       </c>
       <c r="R9" t="n">
-        <v>6923791</v>
+        <v>6923949</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,10 +1584,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129926727</v>
+        <v>129926707</v>
       </c>
       <c r="B10" t="n">
-        <v>79677</v>
+        <v>78846</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1595,21 +1595,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1619,13 +1619,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>444295</v>
+        <v>444272</v>
       </c>
       <c r="R10" t="n">
-        <v>6923949</v>
+        <v>6923791</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,32 +1695,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129926731</v>
+        <v>129926714</v>
       </c>
       <c r="B11" t="n">
-        <v>78845</v>
+        <v>91779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1730,10 +1730,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>444190</v>
+        <v>444331</v>
       </c>
       <c r="R11" t="n">
-        <v>6923908</v>
+        <v>6923827</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1765,7 +1765,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,10 +1806,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129926700</v>
+        <v>129926731</v>
       </c>
       <c r="B12" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,10 +1841,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>444139</v>
+        <v>444190</v>
       </c>
       <c r="R12" t="n">
-        <v>6923624</v>
+        <v>6923908</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,32 +1917,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129926714</v>
+        <v>129926700</v>
       </c>
       <c r="B13" t="n">
-        <v>91778</v>
+        <v>78846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444331</v>
+        <v>444139</v>
       </c>
       <c r="R13" t="n">
-        <v>6923827</v>
+        <v>6923624</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2142,7 +2142,7 @@
         <v>129926729</v>
       </c>
       <c r="B15" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129926718</v>
+        <v>129926705</v>
       </c>
       <c r="B16" t="n">
-        <v>97674</v>
+        <v>80228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,21 +2270,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2294,13 +2294,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444362</v>
+        <v>444117</v>
       </c>
       <c r="R16" t="n">
-        <v>6923872</v>
+        <v>6923735</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129926705</v>
+        <v>129926718</v>
       </c>
       <c r="B17" t="n">
-        <v>80227</v>
+        <v>97675</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2381,21 +2381,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444117</v>
+        <v>444362</v>
       </c>
       <c r="R17" t="n">
-        <v>6923735</v>
+        <v>6923872</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,7 +2484,7 @@
         <v>129926698</v>
       </c>
       <c r="B18" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>129926715</v>
       </c>
       <c r="B19" t="n">
-        <v>92247</v>
+        <v>92248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>129926734</v>
       </c>
       <c r="B20" t="n">
-        <v>78753</v>
+        <v>78754</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129926704</v>
       </c>
       <c r="B21" t="n">
-        <v>80228</v>
+        <v>80229</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>129926710</v>
       </c>
       <c r="B22" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>129926720</v>
       </c>
       <c r="B23" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>129926721</v>
       </c>
       <c r="B24" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3267,48 +3267,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129926724</v>
+        <v>129926706</v>
       </c>
       <c r="B25" t="n">
-        <v>78845</v>
+        <v>90429</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444330</v>
+        <v>444279</v>
       </c>
       <c r="R25" t="n">
-        <v>6923984</v>
+        <v>6923782</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3337,7 +3346,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3347,7 +3356,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,57 +3387,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129926706</v>
+        <v>129926724</v>
       </c>
       <c r="B26" t="n">
-        <v>90428</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6286</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444279</v>
+        <v>444330</v>
       </c>
       <c r="R26" t="n">
-        <v>6923782</v>
+        <v>6923984</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3498,10 +3498,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129926709</v>
+        <v>129926728</v>
       </c>
       <c r="B27" t="n">
-        <v>91528</v>
+        <v>91659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3509,21 +3509,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3533,13 +3533,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444268</v>
+        <v>444229</v>
       </c>
       <c r="R27" t="n">
-        <v>6923829</v>
+        <v>6923882</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3609,57 +3609,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129926702</v>
+        <v>129926709</v>
       </c>
       <c r="B28" t="n">
-        <v>98797</v>
+        <v>91529</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444122</v>
+        <v>444268</v>
       </c>
       <c r="R28" t="n">
-        <v>6923680</v>
+        <v>6923829</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3688,7 +3679,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3698,7 +3689,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3729,32 +3720,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129926728</v>
+        <v>129926701</v>
       </c>
       <c r="B29" t="n">
-        <v>91658</v>
+        <v>105864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2079</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3764,10 +3755,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444229</v>
+        <v>444126</v>
       </c>
       <c r="R29" t="n">
-        <v>6923882</v>
+        <v>6923694</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3799,7 +3790,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3809,7 +3800,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3840,45 +3831,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129926701</v>
+        <v>129926702</v>
       </c>
       <c r="B30" t="n">
-        <v>105863</v>
+        <v>98798</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Högfjället, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444126</v>
+        <v>444122</v>
       </c>
       <c r="R30" t="n">
-        <v>6923694</v>
+        <v>6923680</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3954,7 +3954,7 @@
         <v>129926730</v>
       </c>
       <c r="B31" t="n">
-        <v>78490</v>
+        <v>78491</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>129926733</v>
       </c>
       <c r="B32" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4173,10 +4173,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129926713</v>
+        <v>129926736</v>
       </c>
       <c r="B33" t="n">
-        <v>91528</v>
+        <v>78845</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4184,21 +4184,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3242</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4208,13 +4208,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>444347</v>
+        <v>444093</v>
       </c>
       <c r="R33" t="n">
-        <v>6923828</v>
+        <v>6923866</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4253,12 +4253,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:48</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Under grov, gammal nedfallen tallgren.</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4289,10 +4284,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129926736</v>
+        <v>129926713</v>
       </c>
       <c r="B34" t="n">
-        <v>78844</v>
+        <v>91529</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4300,21 +4295,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>3242</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4324,13 +4319,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444093</v>
+        <v>444347</v>
       </c>
       <c r="R34" t="n">
-        <v>6923866</v>
+        <v>6923828</v>
       </c>
       <c r="S34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4359,7 +4354,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4369,7 +4364,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Under grov, gammal nedfallen tallgren.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4403,7 +4403,7 @@
         <v>129926703</v>
       </c>
       <c r="B35" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         <v>129926717</v>
       </c>
       <c r="B36" t="n">
-        <v>91619</v>
+        <v>91620</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>129926735</v>
       </c>
       <c r="B37" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4742,32 +4742,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129926708</v>
+        <v>129926716</v>
       </c>
       <c r="B38" t="n">
-        <v>79677</v>
+        <v>91779</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4777,10 +4777,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444257</v>
+        <v>444351</v>
       </c>
       <c r="R38" t="n">
-        <v>6923818</v>
+        <v>6923878</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4853,32 +4853,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129926716</v>
+        <v>129926708</v>
       </c>
       <c r="B39" t="n">
-        <v>91778</v>
+        <v>79678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4888,10 +4888,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444351</v>
+        <v>444257</v>
       </c>
       <c r="R39" t="n">
-        <v>6923878</v>
+        <v>6923818</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4933,7 +4933,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
